--- a/excell/ALCO LLC_Aminol_PDS data_ATF.xlsx
+++ b/excell/ALCO LLC_Aminol_PDS data_ATF.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Aminol_label data\Last\Last updated_12.12.2023\Aminol_PDS_database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aytac M\Documents\GitHub\Aminol\excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4347D6EA-E1C5-48D3-98D8-10E86A93CB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ATF" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="62">
   <si>
     <t>Product ID</t>
   </si>
@@ -254,11 +247,14 @@
   <si>
     <t>Aminol™  ATF CVT is recommended for use in the latest generation of Continuously Variable Transmission (CVT) gearboxes, which transfer traction via steel-made traction chain or push-belts. It should not be mixed with other ATF fluids designed for stepped automatic transmissions.</t>
   </si>
+  <si>
+    <t>Application</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -464,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -479,6 +475,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -494,29 +508,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,77 +728,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:L11"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
     <col min="4" max="4" width="59" customWidth="1"/>
     <col min="5" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="22.44140625" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="11" width="70.44140625" customWidth="1"/>
-    <col min="12" max="12" width="24.109375" style="18" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
+    <col min="9" max="10" width="20.28515625" customWidth="1"/>
+    <col min="11" max="11" width="70.42578125" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="F2" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="7"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16" t="s">
+    <row r="3" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="13"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="13"/>
+      <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
@@ -818,26 +813,26 @@
       <c r="F4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="17" t="s">
+      <c r="G4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>26</v>
       </c>
@@ -853,26 +848,26 @@
       <c r="F5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="17" t="s">
+      <c r="G5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
@@ -888,26 +883,26 @@
       <c r="F6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="17" t="s">
+      <c r="G6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
@@ -923,26 +918,26 @@
       <c r="F7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="17" t="s">
+      <c r="G7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
@@ -952,32 +947,32 @@
       <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="17" t="s">
+      <c r="G8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
@@ -993,26 +988,26 @@
       <c r="F9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="17" t="s">
+      <c r="G9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
@@ -1028,26 +1023,26 @@
       <c r="F10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="17" t="s">
+      <c r="G10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>49</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
@@ -1063,22 +1058,22 @@
       <c r="F11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="17" t="s">
+      <c r="G11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="10" t="s">
         <v>40</v>
       </c>
     </row>
